--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>Concepto</t>
   </si>
@@ -50,12 +50,6 @@
     <t>Ordenador</t>
   </si>
   <si>
-    <t>Periféricos
- - Teclado
- - Ratón
- - Pantalla</t>
-  </si>
-  <si>
     <t>AWS S3</t>
   </si>
   <si>
@@ -80,13 +74,46 @@
     <t>Total horas</t>
   </si>
   <si>
-    <t>Tiempo trabajo</t>
-  </si>
-  <si>
     <t>Precio/unidad/mes</t>
   </si>
   <si>
     <t>Meses de uso</t>
+  </si>
+  <si>
+    <t>Programador</t>
+  </si>
+  <si>
+    <t>Arquitecto</t>
+  </si>
+  <si>
+    <t>Analista</t>
+  </si>
+  <si>
+    <t>Diseñador</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Pago/hora</t>
+  </si>
+  <si>
+    <t>Horas</t>
+  </si>
+  <si>
+    <t>Tiempo trabajo Estimado</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Ratón</t>
+  </si>
+  <si>
+    <t>Pantalla</t>
   </si>
 </sst>
 </file>
@@ -96,7 +123,7 @@
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -114,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,8 +154,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -136,24 +169,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -451,185 +558,352 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="8">
         <v>1500</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="10">
         <v>14600</v>
       </c>
-      <c r="E3">
-        <f>C8</f>
+      <c r="E3" s="11">
+        <f>C$14</f>
         <v>540</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="12">
         <f>B3*C3/D3*E3</f>
         <v>55.479452054794514</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="7">
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="15">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="11">
         <v>2</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="11">
         <v>6</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="12">
         <f>I3*J3*K3</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="N3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="14">
+        <v>7.27</v>
+      </c>
+      <c r="P3" s="11">
+        <f>$C$14/100*O13</f>
+        <v>324</v>
+      </c>
+      <c r="Q3" s="16">
+        <f>O3*P3</f>
+        <v>2355.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="14">
+        <v>100</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10">
+        <v>14600</v>
+      </c>
+      <c r="E4" s="11">
+        <f>C$14</f>
+        <v>540</v>
+      </c>
+      <c r="F4" s="12">
+        <f>B4*C4/D4*E4</f>
+        <v>3.6986301369863011</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6">
-        <v>300</v>
-      </c>
-      <c r="C4" s="8">
+      <c r="I4" s="15">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11">
         <v>1</v>
       </c>
-      <c r="D4" s="5">
-        <v>14600</v>
-      </c>
-      <c r="E4">
-        <f>C8</f>
-        <v>540</v>
-      </c>
-      <c r="F4" s="7">
-        <f>B4*C4/D4*E4</f>
-        <v>11.095890410958903</v>
-      </c>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="K4" s="11">
         <v>6</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="12">
         <f t="shared" ref="L4:L5" si="0">I4*J4*K4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="N4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="14">
+        <v>7.27</v>
+      </c>
+      <c r="P4" s="11">
+        <f t="shared" ref="P4:P6" si="1">$C$14/100*O14</f>
+        <v>81</v>
+      </c>
+      <c r="Q4" s="16">
+        <f t="shared" ref="Q4:Q6" si="2">O4*P4</f>
+        <v>588.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="14">
+        <v>50</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>14600</v>
+      </c>
+      <c r="E5" s="11">
+        <f>C$14</f>
+        <v>540</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" ref="F5:F6" si="3">B5*C5/D5*E5</f>
+        <v>1.8493150684931505</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="15">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="11">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="11">
         <v>6</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="N5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="14">
+        <v>7.27</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="Q5" s="16">
+        <f t="shared" si="2"/>
+        <v>588.87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="14">
+        <v>150</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10">
+        <v>14600</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C$14</f>
+        <v>540</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="3"/>
+        <v>5.5479452054794516</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="6">
+        <f>SUM(L3:L5)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="14">
+        <v>7.27</v>
+      </c>
+      <c r="P6" s="11">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="Q6" s="16">
+        <f t="shared" si="2"/>
+        <v>392.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="17">
+        <f>SUM(F3:F4)</f>
+        <v>59.178082191780817</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="6">
+        <f>SUM(Q3:Q6)</f>
+        <v>3925.7999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="N12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="N13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B14" s="4">
         <v>3</v>
       </c>
-      <c r="C8">
-        <f>A8*30*B8</f>
+      <c r="C14" s="5">
+        <f>A14*30*B14</f>
         <v>540</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +911,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>Concepto</t>
   </si>
@@ -38,9 +38,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Material</t>
-  </si>
-  <si>
     <t>Licencias</t>
   </si>
   <si>
@@ -114,6 +111,69 @@
   </si>
   <si>
     <t>Pantalla</t>
+  </si>
+  <si>
+    <t>QA / Tester</t>
+  </si>
+  <si>
+    <t>Jefe de proyecto</t>
+  </si>
+  <si>
+    <t>Dominio</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Visual Studio Code</t>
+  </si>
+  <si>
+    <t>Paint.net</t>
+  </si>
+  <si>
+    <t>Clipchamp</t>
+  </si>
+  <si>
+    <t>Audacity</t>
+  </si>
+  <si>
+    <t>Gimp</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>NestJS</t>
+  </si>
+  <si>
+    <t>Total Neto</t>
+  </si>
+  <si>
+    <t>Total Bruto</t>
+  </si>
+  <si>
+    <t>Impuestos %</t>
+  </si>
+  <si>
+    <t>Inpuestos %</t>
+  </si>
+  <si>
+    <t>Infraestructura tecnológica Mensual</t>
+  </si>
+  <si>
+    <t>Material Mensual</t>
+  </si>
+  <si>
+    <t>Infraestructura tecnológica Anual</t>
+  </si>
+  <si>
+    <t>Años de uso</t>
+  </si>
+  <si>
+    <t>Precio/unidad/año</t>
+  </si>
+  <si>
+    <t>Impuesto %</t>
   </si>
 </sst>
 </file>
@@ -161,27 +221,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="4"/>
-      </left>
-      <right style="medium">
-        <color theme="4"/>
-      </right>
-      <top style="medium">
-        <color theme="4"/>
-      </top>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -238,29 +283,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,377 +599,859 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="B1:AH19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+      <c r="K2" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="19"/>
+      <c r="S2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="19"/>
+      <c r="Z2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="19"/>
+      <c r="AG2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH3" s="13">
+        <f>I8</f>
+        <v>160.43303571428572</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C4" s="6">
+        <v>1500</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>7000</v>
+      </c>
+      <c r="F4" s="9">
+        <f>D$15</f>
+        <v>540</v>
+      </c>
+      <c r="G4" s="12">
+        <f>C4*D4/E4*F4</f>
+        <v>115.71428571428571</v>
+      </c>
+      <c r="H4" s="3">
+        <v>21</v>
+      </c>
+      <c r="I4" s="16">
+        <f>G4+G4*H4/100</f>
+        <v>140.01428571428571</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="12">
+        <v>10</v>
+      </c>
+      <c r="M4" s="9">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="N4" s="9">
+        <v>6</v>
+      </c>
+      <c r="O4" s="12">
+        <f>L4*M4*N4</f>
+        <v>120</v>
+      </c>
+      <c r="P4" s="3">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="16">
+        <f>O4+O4*P4/100</f>
+        <v>145.19999999999999</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="23">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
+        <v>1</v>
+      </c>
+      <c r="V4" s="23">
+        <f>T4*U4</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="24">
+        <f>V4+V4*W4/100</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA4" s="11">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="AB4" s="9">
+        <f>$D$15/100*AA14</f>
+        <v>270</v>
+      </c>
+      <c r="AC4" s="11">
+        <f>AA4*AB4</f>
+        <v>3240</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="24">
+        <f>AC4+AC4*AD4/100</f>
+        <v>4244.3999999999996</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH4" s="13">
+        <f>Q7</f>
+        <v>268.62</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="11">
+        <v>100</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>8800</v>
+      </c>
+      <c r="F5" s="9">
+        <f>D$15</f>
+        <v>540</v>
+      </c>
+      <c r="G5" s="12">
+        <f>C5*D5/E5*F5</f>
+        <v>6.1363636363636367</v>
+      </c>
+      <c r="H5" s="3">
+        <v>21</v>
+      </c>
+      <c r="I5" s="16">
+        <f t="shared" ref="I5:I7" si="0">G5+G5*H5/100</f>
+        <v>7.4250000000000007</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="12">
+        <v>2</v>
+      </c>
+      <c r="M5" s="9">
+        <v>1</v>
+      </c>
+      <c r="N5" s="9">
+        <v>6</v>
+      </c>
+      <c r="O5" s="12">
+        <f t="shared" ref="O5:O6" si="1">L5*M5*N5</f>
+        <v>12</v>
+      </c>
+      <c r="P5" s="3">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="16">
+        <f t="shared" ref="Q5:Q6" si="2">O5+O5*P5/100</f>
+        <v>14.52</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="23">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3">
+        <v>1</v>
+      </c>
+      <c r="V5" s="23">
+        <f t="shared" ref="V5:V11" si="3">T5*U5</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="24">
+        <f t="shared" ref="X5:X11" si="4">V5+V5*W5/100</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="11">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="8">
-        <v>1500</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10">
-        <v>14600</v>
-      </c>
-      <c r="E3" s="11">
-        <f>C$14</f>
+      <c r="AB5" s="9">
+        <f t="shared" ref="AB5:AB9" si="5">$D$15/100*AA15</f>
+        <v>81</v>
+      </c>
+      <c r="AC5" s="11">
+        <f t="shared" ref="AC5:AC9" si="6">AA5*AB5</f>
+        <v>1296</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE5" s="24">
+        <f t="shared" ref="AE5:AE9" si="7">AC5+AC5*AD5/100</f>
+        <v>1697.76</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="13">
+        <f>X12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="11">
+        <v>50</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>8800</v>
+      </c>
+      <c r="F6" s="9">
+        <f>D$15</f>
         <v>540</v>
       </c>
-      <c r="F3" s="12">
-        <f>B3*C3/D3*E3</f>
-        <v>55.479452054794514</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G6" s="12">
+        <f t="shared" ref="G6:G7" si="8">C6*D6/E6*F6</f>
+        <v>3.0681818181818183</v>
+      </c>
+      <c r="H6" s="3">
+        <v>21</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="0"/>
+        <v>3.7125000000000004</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11">
-        <v>2</v>
-      </c>
-      <c r="K3" s="11">
+      <c r="L6" s="12">
+        <v>15</v>
+      </c>
+      <c r="M6" s="9">
+        <v>1</v>
+      </c>
+      <c r="N6" s="9">
         <v>6</v>
       </c>
-      <c r="L3" s="12">
-        <f>I3*J3*K3</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="14">
-        <v>7.27</v>
-      </c>
-      <c r="P3" s="11">
-        <f>$C$14/100*O13</f>
-        <v>324</v>
-      </c>
-      <c r="Q3" s="16">
-        <f>O3*P3</f>
-        <v>2355.48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="14">
-        <v>100</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10">
-        <v>14600</v>
-      </c>
-      <c r="E4" s="11">
-        <f>C$14</f>
-        <v>540</v>
-      </c>
-      <c r="F4" s="12">
-        <f>B4*C4/D4*E4</f>
-        <v>3.6986301369863011</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="15">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11">
-        <v>1</v>
-      </c>
-      <c r="K4" s="11">
-        <v>6</v>
-      </c>
-      <c r="L4" s="12">
-        <f t="shared" ref="L4:L5" si="0">I4*J4*K4</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="14">
-        <v>7.27</v>
-      </c>
-      <c r="P4" s="11">
-        <f t="shared" ref="P4:P6" si="1">$C$14/100*O14</f>
-        <v>81</v>
-      </c>
-      <c r="Q4" s="16">
-        <f t="shared" ref="Q4:Q6" si="2">O4*P4</f>
-        <v>588.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="14">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>14600</v>
-      </c>
-      <c r="E5" s="11">
-        <f>C$14</f>
-        <v>540</v>
-      </c>
-      <c r="F5" s="12">
-        <f t="shared" ref="F5:F6" si="3">B5*C5/D5*E5</f>
-        <v>1.8493150684931505</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="15">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11">
-        <v>1</v>
-      </c>
-      <c r="K5" s="11">
-        <v>6</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" s="14">
-        <v>7.27</v>
-      </c>
-      <c r="P5" s="11">
+      <c r="O6" s="12">
         <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="Q5" s="16">
-        <f t="shared" si="2"/>
-        <v>588.87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="14">
-        <v>150</v>
-      </c>
-      <c r="C6" s="11">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10">
-        <v>14600</v>
-      </c>
-      <c r="E6" s="11">
-        <f>C$14</f>
-        <v>540</v>
-      </c>
-      <c r="F6" s="12">
-        <f t="shared" si="3"/>
-        <v>5.5479452054794516</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="6">
-        <f>SUM(L3:L5)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="3">
         <v>21</v>
-      </c>
-      <c r="O6" s="14">
-        <v>7.27</v>
-      </c>
-      <c r="P6" s="11">
-        <f t="shared" si="1"/>
-        <v>54</v>
       </c>
       <c r="Q6" s="16">
         <f t="shared" si="2"/>
-        <v>392.58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="17">
-        <f>SUM(F3:F4)</f>
-        <v>59.178082191780817</v>
+        <v>108.9</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" s="23">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1</v>
+      </c>
+      <c r="V6" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA6" s="11">
+        <v>15</v>
+      </c>
+      <c r="AB6" s="9">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="AC6" s="11">
+        <f t="shared" si="6"/>
+        <v>810</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE6" s="24">
+        <f t="shared" si="7"/>
+        <v>1061.0999999999999</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="13">
+        <f>AE10</f>
+        <v>9832.86</v>
+      </c>
+    </row>
+    <row r="7" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="11">
+        <v>150</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>10560</v>
+      </c>
+      <c r="F7" s="9">
+        <f>D$15</f>
+        <v>540</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="8"/>
+        <v>7.670454545454545</v>
+      </c>
+      <c r="H7" s="3">
+        <v>21</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="0"/>
+        <v>9.28125</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="6">
-        <f>SUM(Q3:Q6)</f>
-        <v>3925.7999999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="Q7" s="14">
+        <f>SUM(Q4:Q6)</f>
+        <v>268.62</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" s="23">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1</v>
+      </c>
+      <c r="V7" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="11">
+        <v>15</v>
+      </c>
+      <c r="AB7" s="9">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="AC7" s="11">
+        <f t="shared" si="6"/>
+        <v>810</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE7" s="24">
+        <f t="shared" si="7"/>
+        <v>1061.0999999999999</v>
+      </c>
+      <c r="AG7" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="24">
+        <f>SUM(AH3:AH6)</f>
+        <v>10261.913035714286</v>
+      </c>
+    </row>
+    <row r="8" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="14">
+        <f>SUM(I4:I7)</f>
+        <v>160.43303571428572</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="23">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="V8" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA8" s="11">
+        <v>14</v>
+      </c>
+      <c r="AB8" s="9">
+        <f>$D$15/100*AA18</f>
+        <v>54</v>
+      </c>
+      <c r="AC8" s="11">
+        <f>AA8*AB8</f>
+        <v>756</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE8" s="24">
+        <f t="shared" si="7"/>
+        <v>990.36</v>
+      </c>
+    </row>
+    <row r="9" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T9" s="23">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>1</v>
+      </c>
+      <c r="V9" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA9" s="11">
+        <v>22</v>
+      </c>
+      <c r="AB9" s="9">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="AC9" s="11">
+        <f t="shared" si="6"/>
+        <v>594</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>31</v>
+      </c>
+      <c r="AE9" s="24">
+        <f t="shared" si="7"/>
+        <v>778.14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T10" s="23">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1</v>
+      </c>
+      <c r="V10" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="14">
+        <f>SUM(AE4:AE9)</f>
+        <v>9832.86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" s="23">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>1</v>
+      </c>
+      <c r="V11" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="14">
+        <f>SUM(X4:X11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="Z13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA13" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="N12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    </row>
+    <row r="14" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="K14" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="19"/>
+      <c r="Z14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4">
+        <f>B15*30*C15</f>
+        <v>540</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="O15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA15" s="4">
         <v>15</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4">
+    </row>
+    <row r="16" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="12">
+        <v>12</v>
+      </c>
+      <c r="M16" s="9">
+        <v>1</v>
+      </c>
+      <c r="N16" s="9">
+        <v>1</v>
+      </c>
+      <c r="O16" s="12">
+        <f>L16*M16*N16</f>
+        <v>12</v>
+      </c>
+      <c r="P16" s="3">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="16">
+        <f>O16+O16*P16/100</f>
+        <v>14.52</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="5">
-        <f>A14*30*B14</f>
-        <v>540</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N15" s="3" t="s">
+      <c r="Q17" s="14">
+        <f>SUM(Q16)</f>
+        <v>14.52</v>
+      </c>
+      <c r="Z17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O15" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="5">
+      <c r="AA17" s="4">
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A12:C12"/>
+  <mergeCells count="6">
+    <mergeCell ref="K14:Q14"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Z2:AE2"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -283,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -301,10 +301,12 @@
     <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -314,11 +316,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -630,133 +631,133 @@
     <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-      <c r="K2" s="17" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="23"/>
+      <c r="K2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="19"/>
-      <c r="S2" s="17" t="s">
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="23"/>
+      <c r="S2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="19"/>
-      <c r="Z2" s="17" t="s">
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="23"/>
+      <c r="Z2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="19"/>
-      <c r="AG2" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="22" t="s">
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="23"/>
+      <c r="AG2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="21" t="s">
+      <c r="B3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="21" t="s">
+      <c r="K3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="21" t="s">
+      <c r="S3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="V3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="W3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="22" t="s">
+      <c r="X3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Z3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="21" t="s">
+      <c r="Z3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AB3" s="21" t="s">
+      <c r="AB3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AC3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AD3" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="22" t="s">
+      <c r="AE3" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AG3" s="5" t="s">
@@ -791,7 +792,7 @@
       <c r="H4" s="3">
         <v>21</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="15">
         <f>G4+G4*H4/100</f>
         <v>140.01428571428571</v>
       </c>
@@ -814,27 +815,27 @@
       <c r="P4" s="3">
         <v>21</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="15">
         <f>O4+O4*P4/100</f>
         <v>145.19999999999999</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="23">
+      <c r="T4" s="19">
         <v>0</v>
       </c>
       <c r="U4" s="3">
         <v>1</v>
       </c>
-      <c r="V4" s="23">
+      <c r="V4" s="19">
         <f>T4*U4</f>
         <v>0</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
       </c>
-      <c r="X4" s="24">
+      <c r="X4" s="20">
         <f>V4+V4*W4/100</f>
         <v>0</v>
       </c>
@@ -855,7 +856,7 @@
       <c r="AD4" s="3">
         <v>31</v>
       </c>
-      <c r="AE4" s="24">
+      <c r="AE4" s="20">
         <f>AC4+AC4*AD4/100</f>
         <v>4244.3999999999996</v>
       </c>
@@ -891,7 +892,7 @@
       <c r="H5" s="3">
         <v>21</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="15">
         <f t="shared" ref="I5:I7" si="0">G5+G5*H5/100</f>
         <v>7.4250000000000007</v>
       </c>
@@ -914,27 +915,27 @@
       <c r="P5" s="3">
         <v>21</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="15">
         <f t="shared" ref="Q5:Q6" si="2">O5+O5*P5/100</f>
         <v>14.52</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T5" s="23">
+      <c r="T5" s="19">
         <v>0</v>
       </c>
       <c r="U5" s="3">
         <v>1</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="19">
         <f t="shared" ref="V5:V11" si="3">T5*U5</f>
         <v>0</v>
       </c>
       <c r="W5" s="3">
         <v>0</v>
       </c>
-      <c r="X5" s="24">
+      <c r="X5" s="20">
         <f t="shared" ref="X5:X11" si="4">V5+V5*W5/100</f>
         <v>0</v>
       </c>
@@ -955,7 +956,7 @@
       <c r="AD5" s="3">
         <v>31</v>
       </c>
-      <c r="AE5" s="24">
+      <c r="AE5" s="20">
         <f t="shared" ref="AE5:AE9" si="7">AC5+AC5*AD5/100</f>
         <v>1697.76</v>
       </c>
@@ -991,7 +992,7 @@
       <c r="H6" s="3">
         <v>21</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="15">
         <f t="shared" si="0"/>
         <v>3.7125000000000004</v>
       </c>
@@ -1014,27 +1015,27 @@
       <c r="P6" s="3">
         <v>21</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="15">
         <f t="shared" si="2"/>
         <v>108.9</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="23">
+      <c r="T6" s="19">
         <v>0</v>
       </c>
       <c r="U6" s="3">
         <v>1</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W6" s="3">
         <v>0</v>
       </c>
-      <c r="X6" s="24">
+      <c r="X6" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1055,7 +1056,7 @@
       <c r="AD6" s="3">
         <v>31</v>
       </c>
-      <c r="AE6" s="24">
+      <c r="AE6" s="20">
         <f t="shared" si="7"/>
         <v>1061.0999999999999</v>
       </c>
@@ -1091,10 +1092,15 @@
       <c r="H7" s="3">
         <v>21</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
         <v>9.28125</v>
       </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
       <c r="P7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1105,20 +1111,20 @@
       <c r="S7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T7" s="23">
+      <c r="T7" s="19">
         <v>0</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W7" s="3">
         <v>0</v>
       </c>
-      <c r="X7" s="24">
+      <c r="X7" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1139,19 +1145,25 @@
       <c r="AD7" s="3">
         <v>31</v>
       </c>
-      <c r="AE7" s="24">
+      <c r="AE7" s="20">
         <f t="shared" si="7"/>
         <v>1061.0999999999999</v>
       </c>
-      <c r="AG7" s="20" t="s">
+      <c r="AG7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="AH7" s="24">
+      <c r="AH7" s="20">
         <f>SUM(AH3:AH6)</f>
         <v>10261.913035714286</v>
       </c>
     </row>
     <row r="8" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1162,20 +1174,20 @@
       <c r="S8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T8" s="23">
+      <c r="T8" s="19">
         <v>0</v>
       </c>
       <c r="U8" s="3">
         <v>1</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-      <c r="X8" s="24">
+      <c r="X8" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1196,7 +1208,7 @@
       <c r="AD8" s="3">
         <v>31</v>
       </c>
-      <c r="AE8" s="24">
+      <c r="AE8" s="20">
         <f t="shared" si="7"/>
         <v>990.36</v>
       </c>
@@ -1205,20 +1217,20 @@
       <c r="S9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T9" s="23">
+      <c r="T9" s="19">
         <v>0</v>
       </c>
       <c r="U9" s="3">
         <v>1</v>
       </c>
-      <c r="V9" s="23">
+      <c r="V9" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
-      <c r="X9" s="24">
+      <c r="X9" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1239,7 +1251,7 @@
       <c r="AD9" s="3">
         <v>31</v>
       </c>
-      <c r="AE9" s="24">
+      <c r="AE9" s="20">
         <f t="shared" si="7"/>
         <v>778.14</v>
       </c>
@@ -1248,23 +1260,27 @@
       <c r="S10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T10" s="23">
+      <c r="T10" s="19">
         <v>0</v>
       </c>
       <c r="U10" s="3">
         <v>1</v>
       </c>
-      <c r="V10" s="23">
+      <c r="V10" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
-      <c r="X10" s="24">
+      <c r="X10" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
       <c r="AD10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1277,25 +1293,29 @@
       <c r="S11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="T11" s="23">
+      <c r="T11" s="19">
         <v>0</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
       </c>
-      <c r="V11" s="23">
+      <c r="V11" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W11" s="3">
         <v>0</v>
       </c>
-      <c r="X11" s="24">
+      <c r="X11" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
       <c r="W12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1305,15 +1325,15 @@
       </c>
     </row>
     <row r="13" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="Z13" s="20" t="s">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="Z13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AA13" s="22" t="s">
+      <c r="AA13" s="18" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1327,15 +1347,15 @@
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="19"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="23"/>
       <c r="Z14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1354,25 +1374,25 @@
         <f>B15*30*C15</f>
         <v>540</v>
       </c>
-      <c r="K15" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="L15" s="21" t="s">
+      <c r="K15" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="21" t="s">
+      <c r="M15" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="N15" s="21" t="s">
+      <c r="N15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O15" s="21" t="s">
+      <c r="O15" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="P15" s="21" t="s">
+      <c r="P15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="Q15" s="22" t="s">
+      <c r="Q15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="Z15" s="2" t="s">
@@ -1402,7 +1422,7 @@
       <c r="P16" s="3">
         <v>21</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="15">
         <f>O16+O16*P16/100</f>
         <v>14.52</v>
       </c>

--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -307,6 +307,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -319,7 +320,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,41 +636,41 @@
   <sheetData>
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="23"/>
-      <c r="K2" s="21" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="24"/>
+      <c r="K2" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="23"/>
-      <c r="S2" s="21" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="24"/>
+      <c r="S2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="23"/>
-      <c r="Z2" s="21" t="s">
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="24"/>
+      <c r="Z2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="24"/>
       <c r="AG2" s="16" t="s">
         <v>0</v>
       </c>
@@ -1096,11 +1096,11 @@
         <f t="shared" si="0"/>
         <v>9.28125</v>
       </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
       <c r="P7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1158,12 +1158,12 @@
       </c>
     </row>
     <row r="8" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
       <c r="H8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1277,10 +1277,10 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="21"/>
       <c r="AD10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1312,10 +1312,10 @@
       </c>
     </row>
     <row r="12" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
       <c r="W12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1325,11 +1325,11 @@
       </c>
     </row>
     <row r="13" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
       <c r="Z13" s="16" t="s">
         <v>21</v>
       </c>
@@ -1347,15 +1347,15 @@
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="24"/>
       <c r="Z14" s="2" t="s">
         <v>17</v>
       </c>

--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>Concepto</t>
   </si>
@@ -62,15 +62,6 @@
     <t>Necesidad de uso / h</t>
   </si>
   <si>
-    <t>Meses</t>
-  </si>
-  <si>
-    <t>Horas/día</t>
-  </si>
-  <si>
-    <t>Total horas</t>
-  </si>
-  <si>
     <t>Precio/unidad/mes</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
   </si>
   <si>
     <t>Horas</t>
-  </si>
-  <si>
-    <t>Tiempo trabajo Estimado</t>
   </si>
   <si>
     <t>Porcentaje</t>
@@ -637,7 +625,7 @@
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -647,7 +635,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="24"/>
       <c r="K2" s="22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="23"/>
@@ -695,34 +683,34 @@
         <v>11</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>0</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P3" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>0</v>
@@ -734,38 +722,38 @@
         <v>2</v>
       </c>
       <c r="V3" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="X3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG3" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC3" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD3" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE3" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG3" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="AH3" s="13">
         <f>I8</f>
-        <v>160.43303571428572</v>
+        <v>71.303571428571431</v>
       </c>
     </row>
     <row r="4" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -783,18 +771,18 @@
       </c>
       <c r="F4" s="9">
         <f>D$15</f>
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G4" s="12">
         <f>C4*D4/E4*F4</f>
-        <v>115.71428571428571</v>
+        <v>51.428571428571423</v>
       </c>
       <c r="H4" s="3">
         <v>21</v>
       </c>
       <c r="I4" s="15">
         <f>G4+G4*H4/100</f>
-        <v>140.01428571428571</v>
+        <v>62.228571428571428</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>8</v>
@@ -820,7 +808,7 @@
         <v>145.19999999999999</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T4" s="19">
         <v>0</v>
@@ -840,28 +828,28 @@
         <v>0</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA4" s="11">
         <v>12</v>
       </c>
       <c r="AB4" s="9">
         <f>$D$15/100*AA14</f>
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="AC4" s="11">
         <f>AA4*AB4</f>
-        <v>3240</v>
+        <v>1440</v>
       </c>
       <c r="AD4" s="3">
         <v>31</v>
       </c>
       <c r="AE4" s="20">
         <f>AC4+AC4*AD4/100</f>
-        <v>4244.3999999999996</v>
+        <v>1886.4</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH4" s="13">
         <f>Q7</f>
@@ -870,7 +858,7 @@
     </row>
     <row r="5" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" s="11">
         <v>100</v>
@@ -883,18 +871,18 @@
       </c>
       <c r="F5" s="9">
         <f>D$15</f>
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G5" s="12">
         <f>C5*D5/E5*F5</f>
-        <v>6.1363636363636367</v>
+        <v>2.7272727272727275</v>
       </c>
       <c r="H5" s="3">
         <v>21</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" ref="I5:I7" si="0">G5+G5*H5/100</f>
-        <v>7.4250000000000007</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>7</v>
@@ -920,7 +908,7 @@
         <v>14.52</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="T5" s="19">
         <v>0</v>
@@ -940,25 +928,25 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA5" s="11">
         <v>16</v>
       </c>
       <c r="AB5" s="9">
         <f t="shared" ref="AB5:AB9" si="5">$D$15/100*AA15</f>
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="AC5" s="11">
         <f t="shared" ref="AC5:AC9" si="6">AA5*AB5</f>
-        <v>1296</v>
+        <v>576</v>
       </c>
       <c r="AD5" s="3">
         <v>31</v>
       </c>
       <c r="AE5" s="20">
         <f t="shared" ref="AE5:AE9" si="7">AC5+AC5*AD5/100</f>
-        <v>1697.76</v>
+        <v>754.56</v>
       </c>
       <c r="AG5" s="5" t="s">
         <v>4</v>
@@ -970,7 +958,7 @@
     </row>
     <row r="6" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="11">
         <v>50</v>
@@ -983,18 +971,18 @@
       </c>
       <c r="F6" s="9">
         <f>D$15</f>
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" ref="G6:G7" si="8">C6*D6/E6*F6</f>
-        <v>3.0681818181818183</v>
+        <v>1.3636363636363638</v>
       </c>
       <c r="H6" s="3">
         <v>21</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="0"/>
-        <v>3.7125000000000004</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>9</v>
@@ -1020,7 +1008,7 @@
         <v>108.9</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="T6" s="19">
         <v>0</v>
@@ -1040,37 +1028,37 @@
         <v>0</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="11">
         <v>15</v>
       </c>
       <c r="AB6" s="9">
         <f t="shared" si="5"/>
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="AC6" s="11">
         <f t="shared" si="6"/>
-        <v>810</v>
+        <v>360</v>
       </c>
       <c r="AD6" s="3">
         <v>31</v>
       </c>
       <c r="AE6" s="20">
         <f t="shared" si="7"/>
-        <v>1061.0999999999999</v>
+        <v>471.6</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="AH6" s="13">
         <f>AE10</f>
-        <v>9832.86</v>
+        <v>4370.16</v>
       </c>
     </row>
     <row r="7" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="11">
         <v>150</v>
@@ -1083,18 +1071,18 @@
       </c>
       <c r="F7" s="9">
         <f>D$15</f>
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" si="8"/>
-        <v>7.670454545454545</v>
+        <v>3.4090909090909092</v>
       </c>
       <c r="H7" s="3">
         <v>21</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>9.28125</v>
+        <v>4.125</v>
       </c>
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
@@ -1109,7 +1097,7 @@
         <v>268.62</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T7" s="19">
         <v>0</v>
@@ -1129,32 +1117,32 @@
         <v>0</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="11">
         <v>15</v>
       </c>
       <c r="AB7" s="9">
         <f t="shared" si="5"/>
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="AC7" s="11">
         <f t="shared" si="6"/>
-        <v>810</v>
+        <v>360</v>
       </c>
       <c r="AD7" s="3">
         <v>31</v>
       </c>
       <c r="AE7" s="20">
         <f t="shared" si="7"/>
-        <v>1061.0999999999999</v>
+        <v>471.6</v>
       </c>
       <c r="AG7" s="16" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="20">
         <f>SUM(AH3:AH6)</f>
-        <v>10261.913035714286</v>
+        <v>4710.0835714285713</v>
       </c>
     </row>
     <row r="8" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1169,10 +1157,10 @@
       </c>
       <c r="I8" s="14">
         <f>SUM(I4:I7)</f>
-        <v>160.43303571428572</v>
+        <v>71.303571428571431</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="T8" s="19">
         <v>0</v>
@@ -1192,30 +1180,30 @@
         <v>0</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA8" s="11">
         <v>14</v>
       </c>
       <c r="AB8" s="9">
         <f>$D$15/100*AA18</f>
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="AC8" s="11">
         <f>AA8*AB8</f>
-        <v>756</v>
+        <v>336</v>
       </c>
       <c r="AD8" s="3">
         <v>31</v>
       </c>
       <c r="AE8" s="20">
         <f t="shared" si="7"/>
-        <v>990.36</v>
+        <v>440.15999999999997</v>
       </c>
     </row>
     <row r="9" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="S9" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="T9" s="19">
         <v>0</v>
@@ -1235,30 +1223,30 @@
         <v>0</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA9" s="11">
         <v>22</v>
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AC9" s="11">
         <f t="shared" si="6"/>
-        <v>594</v>
+        <v>264</v>
       </c>
       <c r="AD9" s="3">
         <v>31</v>
       </c>
       <c r="AE9" s="20">
         <f t="shared" si="7"/>
-        <v>778.14</v>
+        <v>345.84000000000003</v>
       </c>
     </row>
     <row r="10" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="S10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T10" s="19">
         <v>0</v>
@@ -1286,12 +1274,12 @@
       </c>
       <c r="AE10" s="14">
         <f>SUM(AE4:AE9)</f>
-        <v>9832.86</v>
+        <v>4370.16</v>
       </c>
     </row>
     <row r="11" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="S11" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="T11" s="19">
         <v>0</v>
@@ -1325,30 +1313,22 @@
       </c>
     </row>
     <row r="13" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
-        <v>24</v>
-      </c>
+      <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="Z13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="AA13" s="18" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="14" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
       <c r="K14" s="22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
@@ -1357,46 +1337,41 @@
       <c r="P14" s="23"/>
       <c r="Q14" s="24"/>
       <c r="Z14" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA14" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="4">
-        <f>B15*30*C15</f>
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M15" s="17" t="s">
         <v>2</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA15" s="4">
         <v>15</v>
@@ -1404,7 +1379,7 @@
     </row>
     <row r="16" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K16" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12">
         <v>12</v>
@@ -1427,13 +1402,18 @@
         <v>14.52</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA16" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
       <c r="P17" s="1" t="s">
         <v>3</v>
       </c>
@@ -1442,23 +1422,23 @@
         <v>14.52</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA17" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Z18" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA18" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="16:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Z19" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA19" s="4">
         <v>5</v>

--- a/Proyecto Intermodular/Presupuestos.xlsx
+++ b/Proyecto Intermodular/Presupuestos.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alberto\Documents\GitHub\2-DAW\Proyecto Intermodular\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24810"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -167,13 +162,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,7 +363,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -403,7 +398,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -580,16 +575,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:AH19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
@@ -622,8 +617,8 @@
     <col min="34" max="34" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:34" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:34" ht="15.75" thickBot="1">
       <c r="B2" s="22" t="s">
         <v>41</v>
       </c>
@@ -666,7 +661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:34" ht="15.75" thickBot="1">
       <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
@@ -753,10 +748,10 @@
       </c>
       <c r="AH3" s="13">
         <f>I8</f>
-        <v>71.303571428571431</v>
-      </c>
-    </row>
-    <row r="4" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>68.332589285714292</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" ht="15.75" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
@@ -771,18 +766,18 @@
       </c>
       <c r="F4" s="9">
         <f>D$15</f>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G4" s="12">
         <f>C4*D4/E4*F4</f>
-        <v>51.428571428571423</v>
+        <v>49.285714285714285</v>
       </c>
       <c r="H4" s="3">
         <v>21</v>
       </c>
       <c r="I4" s="15">
         <f>G4+G4*H4/100</f>
-        <v>62.228571428571428</v>
+        <v>59.635714285714286</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>8</v>
@@ -835,18 +830,18 @@
       </c>
       <c r="AB4" s="9">
         <f>$D$15/100*AA14</f>
-        <v>120</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="AC4" s="11">
         <f>AA4*AB4</f>
-        <v>1440</v>
+        <v>1379.9999999999998</v>
       </c>
       <c r="AD4" s="3">
         <v>31</v>
       </c>
       <c r="AE4" s="20">
         <f>AC4+AC4*AD4/100</f>
-        <v>1886.4</v>
+        <v>1807.7999999999997</v>
       </c>
       <c r="AG4" s="5" t="s">
         <v>40</v>
@@ -856,7 +851,7 @@
         <v>268.62</v>
       </c>
     </row>
-    <row r="5" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:34" ht="15.75" thickBot="1">
       <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
@@ -871,18 +866,18 @@
       </c>
       <c r="F5" s="9">
         <f>D$15</f>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G5" s="12">
         <f>C5*D5/E5*F5</f>
-        <v>2.7272727272727275</v>
+        <v>2.6136363636363638</v>
       </c>
       <c r="H5" s="3">
         <v>21</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" ref="I5:I7" si="0">G5+G5*H5/100</f>
-        <v>3.3000000000000003</v>
+        <v>3.1625000000000001</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>7</v>
@@ -935,18 +930,18 @@
       </c>
       <c r="AB5" s="9">
         <f t="shared" ref="AB5:AB9" si="5">$D$15/100*AA15</f>
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="AC5" s="11">
         <f t="shared" ref="AC5:AC9" si="6">AA5*AB5</f>
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="AD5" s="3">
         <v>31</v>
       </c>
       <c r="AE5" s="20">
         <f t="shared" ref="AE5:AE9" si="7">AC5+AC5*AD5/100</f>
-        <v>754.56</v>
+        <v>723.12</v>
       </c>
       <c r="AG5" s="5" t="s">
         <v>4</v>
@@ -956,7 +951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:34" ht="15.75" thickBot="1">
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
@@ -971,18 +966,18 @@
       </c>
       <c r="F6" s="9">
         <f>D$15</f>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" ref="G6:G7" si="8">C6*D6/E6*F6</f>
-        <v>1.3636363636363638</v>
+        <v>1.3068181818181819</v>
       </c>
       <c r="H6" s="3">
         <v>21</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="0"/>
-        <v>1.6500000000000001</v>
+        <v>1.58125</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>9</v>
@@ -1035,28 +1030,28 @@
       </c>
       <c r="AB6" s="9">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC6" s="11">
         <f t="shared" si="6"/>
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AD6" s="3">
         <v>31</v>
       </c>
       <c r="AE6" s="20">
         <f t="shared" si="7"/>
-        <v>471.6</v>
+        <v>451.95</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="AH6" s="13">
         <f>AE10</f>
-        <v>4370.16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4188.07</v>
+      </c>
+    </row>
+    <row r="7" spans="2:34" ht="15.75" thickBot="1">
       <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
@@ -1071,18 +1066,18 @@
       </c>
       <c r="F7" s="9">
         <f>D$15</f>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" si="8"/>
-        <v>3.4090909090909092</v>
+        <v>3.2670454545454546</v>
       </c>
       <c r="H7" s="3">
         <v>21</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>4.125</v>
+        <v>3.953125</v>
       </c>
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
@@ -1124,28 +1119,28 @@
       </c>
       <c r="AB7" s="9">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC7" s="11">
         <f t="shared" si="6"/>
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AD7" s="3">
         <v>31</v>
       </c>
       <c r="AE7" s="20">
         <f t="shared" si="7"/>
-        <v>471.6</v>
+        <v>451.95</v>
       </c>
       <c r="AG7" s="16" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="20">
         <f>SUM(AH3:AH6)</f>
-        <v>4710.0835714285713</v>
-      </c>
-    </row>
-    <row r="8" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4525.0225892857143</v>
+      </c>
+    </row>
+    <row r="8" spans="2:34" ht="15.75" thickBot="1">
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
@@ -1157,7 +1152,7 @@
       </c>
       <c r="I8" s="14">
         <f>SUM(I4:I7)</f>
-        <v>71.303571428571431</v>
+        <v>68.332589285714292</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>32</v>
@@ -1187,21 +1182,21 @@
       </c>
       <c r="AB8" s="9">
         <f>$D$15/100*AA18</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC8" s="11">
         <f>AA8*AB8</f>
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="AD8" s="3">
         <v>31</v>
       </c>
       <c r="AE8" s="20">
         <f t="shared" si="7"/>
-        <v>440.15999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>421.82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:34" ht="15.75" thickBot="1">
       <c r="S9" s="2" t="s">
         <v>33</v>
       </c>
@@ -1230,21 +1225,21 @@
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" s="11">
         <f t="shared" si="6"/>
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AD9" s="3">
         <v>31</v>
       </c>
       <c r="AE9" s="20">
         <f t="shared" si="7"/>
-        <v>345.84000000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>331.43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:34" ht="15.75" thickBot="1">
       <c r="S10" s="2" t="s">
         <v>34</v>
       </c>
@@ -1274,10 +1269,10 @@
       </c>
       <c r="AE10" s="14">
         <f>SUM(AE4:AE9)</f>
-        <v>4370.16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4188.07</v>
+      </c>
+    </row>
+    <row r="11" spans="2:34" ht="15.75" thickBot="1">
       <c r="S11" s="2" t="s">
         <v>35</v>
       </c>
@@ -1299,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:34" ht="15.75" thickBot="1">
       <c r="S12" s="21"/>
       <c r="T12" s="21"/>
       <c r="U12" s="21"/>
@@ -1312,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:34" ht="15.75" thickBot="1">
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -1323,7 +1318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:34" ht="15.75" thickBot="1">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1343,11 +1338,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:34" ht="15.75" thickBot="1">
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>0</v>
@@ -1377,7 +1372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:34" ht="15.75" thickBot="1">
       <c r="K16" s="5" t="s">
         <v>27</v>
       </c>
@@ -1408,7 +1403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="11:27" ht="15.75" thickBot="1">
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
@@ -1428,7 +1423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="11:27" ht="15.75" thickBot="1">
       <c r="Z18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1436,7 +1431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="11:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="11:27" ht="15.75" thickBot="1">
       <c r="Z19" s="2" t="s">
         <v>26</v>
       </c>
